--- a/feedback_forms/032_tuition_and_fundraising_survey--feedback_forms.xlsx
+++ b/feedback_forms/032_tuition_and_fundraising_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Form Category Label</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Form Description Label</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>input_tuition_rate</t>
+          <t>input_tuition_rate_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tuition rate</t>
+          <t>Input Tuition Rate 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>input_fundraising_effort</t>
+          <t>input_fundraising_effort_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fundraising effort</t>
+          <t>Input Fundraising Effort 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1211,7 +1211,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>input_fundraising_effort_choices</t>
+          <t>input_fundraising_effort_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1228,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>input_fundraising_effort_choices</t>
+          <t>input_fundraising_effort_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>input_fundraising_effort_choices</t>
+          <t>input_fundraising_effort_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
